--- a/2b0ba7d73c6d/KARE2-grafik-2026-09-23.xlsx
+++ b/2b0ba7d73c6d/KARE2-grafik-2026-09-23.xlsx
@@ -4,7 +4,7 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Помощь" sheetId="1" state="visible" r:id="rId1"/>
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlfn_AGGREGATE" hidden="0" function="0" vbProcedure="0">#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'График по датам'!$B$1:$AV$43</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'График по датам'!$B$1:$AX$43</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001"/>
 </workbook>
@@ -32,7 +32,7 @@
     <numFmt numFmtId="172" formatCode="_-* #,##0.00[$€-1]_-;\-* #,##0.00[$€-1]_-;_-* \-??[$€-1]_-"/>
     <numFmt numFmtId="173" formatCode="#,##0&quot; Kз&quot;;\-#,##0&quot; Kз&quot;"/>
     <numFmt numFmtId="174" formatCode="_-* #,##0.00_т_._-;\-* #,##0.00_т_._-;_-* \-??_т_._-;_-@_-"/>
-    <numFmt numFmtId="175" formatCode="d"/>
+    <numFmt numFmtId="175" formatCode="[$-419]mmm\.yy;@"/>
     <numFmt numFmtId="176" formatCode="0;-0;;@"/>
   </numFmts>
   <fonts count="23">
@@ -687,14 +687,14 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="57">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="175" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="175" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="175" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
@@ -1468,9 +1468,9 @@
     <col width="11.13" customWidth="1" style="83" min="12" max="12"/>
     <col width="6.85" customWidth="1" style="83" min="13" max="13"/>
     <col width="11.28" customWidth="1" style="83" min="14" max="14"/>
-    <col width="2.85" customWidth="1" style="83" min="15" max="42"/>
-    <col width="2.85" customWidth="1" style="61" min="43" max="48"/>
-    <col hidden="1" width="2.85" customWidth="1" style="61" min="49" max="86"/>
+    <col width="4" customWidth="1" style="83" min="15" max="42"/>
+    <col width="4" customWidth="1" style="61" min="43" max="48"/>
+    <col hidden="1" width="4" customWidth="1" style="61" min="49" max="86"/>
     <col width="9.130000000000001" customWidth="1" style="61" min="87" max="257"/>
   </cols>
   <sheetData>
@@ -1693,63 +1693,63 @@
       <c r="AV3" s="74" t="n"/>
       <c r="AW3" s="74" t="n"/>
       <c r="AX3" s="75" t="n"/>
-      <c r="AY3" s="76">
+      <c r="AY3" s="93">
         <f>(AY5+AZ5+BA5+BB5)/4</f>
         <v/>
       </c>
       <c r="AZ3" s="74" t="n"/>
       <c r="BA3" s="74" t="n"/>
       <c r="BB3" s="75" t="n"/>
-      <c r="BC3" s="76">
+      <c r="BC3" s="93">
         <f>(BC5+BD5+BE5+BF5)/4</f>
         <v/>
       </c>
       <c r="BD3" s="74" t="n"/>
       <c r="BE3" s="74" t="n"/>
       <c r="BF3" s="75" t="n"/>
-      <c r="BG3" s="76">
+      <c r="BG3" s="93">
         <f>(BG5+BH5+BI5+BJ5)/4</f>
         <v/>
       </c>
       <c r="BH3" s="74" t="n"/>
       <c r="BI3" s="74" t="n"/>
       <c r="BJ3" s="75" t="n"/>
-      <c r="BK3" s="76">
+      <c r="BK3" s="93">
         <f>(BK5+BL5+BM5+BN5)/4</f>
         <v/>
       </c>
       <c r="BL3" s="74" t="n"/>
       <c r="BM3" s="74" t="n"/>
       <c r="BN3" s="75" t="n"/>
-      <c r="BO3" s="76">
+      <c r="BO3" s="93">
         <f>(BO5+BP5+BQ5+BR5)/4</f>
         <v/>
       </c>
       <c r="BP3" s="74" t="n"/>
       <c r="BQ3" s="74" t="n"/>
       <c r="BR3" s="75" t="n"/>
-      <c r="BS3" s="76">
+      <c r="BS3" s="93">
         <f>(BS5+BT5+BU5+BV5)/4</f>
         <v/>
       </c>
       <c r="BT3" s="74" t="n"/>
       <c r="BU3" s="74" t="n"/>
       <c r="BV3" s="75" t="n"/>
-      <c r="BW3" s="76">
+      <c r="BW3" s="93">
         <f>(BW5+BX5+BY5+BZ5)/4</f>
         <v/>
       </c>
       <c r="BX3" s="74" t="n"/>
       <c r="BY3" s="74" t="n"/>
       <c r="BZ3" s="75" t="n"/>
-      <c r="CA3" s="76">
+      <c r="CA3" s="93">
         <f>(CA5+CB5+CC5+CD5)/4</f>
         <v/>
       </c>
       <c r="CB3" s="74" t="n"/>
       <c r="CC3" s="74" t="n"/>
       <c r="CD3" s="75" t="n"/>
-      <c r="CE3" s="76">
+      <c r="CE3" s="93">
         <f>(CE5+CF5+CG5+CH5)/4</f>
         <v/>
       </c>
@@ -1804,147 +1804,147 @@
           <t>Оконч.</t>
         </is>
       </c>
-      <c r="O4" s="93">
+      <c r="O4" s="94">
         <f>LOOKUP(WEEKDAY(O5,2),{1,2,3,4,5,6,7},{"пн","вт","ср","чт","пт","сб","вс"})</f>
         <v/>
       </c>
-      <c r="P4" s="93">
+      <c r="P4" s="94">
         <f>LOOKUP(WEEKDAY(P5,2),{1,2,3,4,5,6,7},{"пн","вт","ср","чт","пт","сб","вс"})</f>
         <v/>
       </c>
-      <c r="Q4" s="93">
+      <c r="Q4" s="94">
         <f>LOOKUP(WEEKDAY(Q5,2),{1,2,3,4,5,6,7},{"пн","вт","ср","чт","пт","сб","вс"})</f>
         <v/>
       </c>
-      <c r="R4" s="93">
+      <c r="R4" s="94">
         <f>LOOKUP(WEEKDAY(R5,2),{1,2,3,4,5,6,7},{"пн","вт","ср","чт","пт","сб","вс"})</f>
         <v/>
       </c>
-      <c r="S4" s="93">
+      <c r="S4" s="94">
         <f>LOOKUP(WEEKDAY(S5,2),{1,2,3,4,5,6,7},{"пн","вт","ср","чт","пт","сб","вс"})</f>
         <v/>
       </c>
-      <c r="T4" s="93">
+      <c r="T4" s="94">
         <f>LOOKUP(WEEKDAY(T5,2),{1,2,3,4,5,6,7},{"пн","вт","ср","чт","пт","сб","вс"})</f>
         <v/>
       </c>
-      <c r="U4" s="93">
+      <c r="U4" s="94">
         <f>LOOKUP(WEEKDAY(U5,2),{1,2,3,4,5,6,7},{"пн","вт","ср","чт","пт","сб","вс"})</f>
         <v/>
       </c>
-      <c r="V4" s="93">
+      <c r="V4" s="94">
         <f>LOOKUP(WEEKDAY(V5,2),{1,2,3,4,5,6,7},{"пн","вт","ср","чт","пт","сб","вс"})</f>
         <v/>
       </c>
-      <c r="W4" s="93">
+      <c r="W4" s="94">
         <f>LOOKUP(WEEKDAY(W5,2),{1,2,3,4,5,6,7},{"пн","вт","ср","чт","пт","сб","вс"})</f>
         <v/>
       </c>
-      <c r="X4" s="93">
+      <c r="X4" s="94">
         <f>LOOKUP(WEEKDAY(X5,2),{1,2,3,4,5,6,7},{"пн","вт","ср","чт","пт","сб","вс"})</f>
         <v/>
       </c>
-      <c r="Y4" s="93">
+      <c r="Y4" s="94">
         <f>LOOKUP(WEEKDAY(Y5,2),{1,2,3,4,5,6,7},{"пн","вт","ср","чт","пт","сб","вс"})</f>
         <v/>
       </c>
-      <c r="Z4" s="93">
+      <c r="Z4" s="94">
         <f>LOOKUP(WEEKDAY(Z5,2),{1,2,3,4,5,6,7},{"пн","вт","ср","чт","пт","сб","вс"})</f>
         <v/>
       </c>
-      <c r="AA4" s="93">
+      <c r="AA4" s="94">
         <f>LOOKUP(WEEKDAY(AA5,2),{1,2,3,4,5,6,7},{"пн","вт","ср","чт","пт","сб","вс"})</f>
         <v/>
       </c>
-      <c r="AB4" s="93">
+      <c r="AB4" s="94">
         <f>LOOKUP(WEEKDAY(AB5,2),{1,2,3,4,5,6,7},{"пн","вт","ср","чт","пт","сб","вс"})</f>
         <v/>
       </c>
-      <c r="AC4" s="93">
+      <c r="AC4" s="94">
         <f>LOOKUP(WEEKDAY(AC5,2),{1,2,3,4,5,6,7},{"пн","вт","ср","чт","пт","сб","вс"})</f>
         <v/>
       </c>
-      <c r="AD4" s="93">
+      <c r="AD4" s="94">
         <f>LOOKUP(WEEKDAY(AD5,2),{1,2,3,4,5,6,7},{"пн","вт","ср","чт","пт","сб","вс"})</f>
         <v/>
       </c>
-      <c r="AE4" s="93">
+      <c r="AE4" s="94">
         <f>LOOKUP(WEEKDAY(AE5,2),{1,2,3,4,5,6,7},{"пн","вт","ср","чт","пт","сб","вс"})</f>
         <v/>
       </c>
-      <c r="AF4" s="93">
+      <c r="AF4" s="94">
         <f>LOOKUP(WEEKDAY(AF5,2),{1,2,3,4,5,6,7},{"пн","вт","ср","чт","пт","сб","вс"})</f>
         <v/>
       </c>
-      <c r="AG4" s="93">
+      <c r="AG4" s="94">
         <f>LOOKUP(WEEKDAY(AG5,2),{1,2,3,4,5,6,7},{"пн","вт","ср","чт","пт","сб","вс"})</f>
         <v/>
       </c>
-      <c r="AH4" s="93">
+      <c r="AH4" s="94">
         <f>LOOKUP(WEEKDAY(AH5,2),{1,2,3,4,5,6,7},{"пн","вт","ср","чт","пт","сб","вс"})</f>
         <v/>
       </c>
-      <c r="AI4" s="93">
+      <c r="AI4" s="94">
         <f>LOOKUP(WEEKDAY(AI5,2),{1,2,3,4,5,6,7},{"пн","вт","ср","чт","пт","сб","вс"})</f>
         <v/>
       </c>
-      <c r="AJ4" s="93">
+      <c r="AJ4" s="94">
         <f>LOOKUP(WEEKDAY(AJ5,2),{1,2,3,4,5,6,7},{"пн","вт","ср","чт","пт","сб","вс"})</f>
         <v/>
       </c>
-      <c r="AK4" s="93">
+      <c r="AK4" s="94">
         <f>LOOKUP(WEEKDAY(AK5,2),{1,2,3,4,5,6,7},{"пн","вт","ср","чт","пт","сб","вс"})</f>
         <v/>
       </c>
-      <c r="AL4" s="93">
+      <c r="AL4" s="94">
         <f>LOOKUP(WEEKDAY(AL5,2),{1,2,3,4,5,6,7},{"пн","вт","ср","чт","пт","сб","вс"})</f>
         <v/>
       </c>
-      <c r="AM4" s="93">
+      <c r="AM4" s="94">
         <f>LOOKUP(WEEKDAY(AM5,2),{1,2,3,4,5,6,7},{"пн","вт","ср","чт","пт","сб","вс"})</f>
         <v/>
       </c>
-      <c r="AN4" s="93">
+      <c r="AN4" s="94">
         <f>LOOKUP(WEEKDAY(AN5,2),{1,2,3,4,5,6,7},{"пн","вт","ср","чт","пт","сб","вс"})</f>
         <v/>
       </c>
-      <c r="AO4" s="93">
+      <c r="AO4" s="94">
         <f>LOOKUP(WEEKDAY(AO5,2),{1,2,3,4,5,6,7},{"пн","вт","ср","чт","пт","сб","вс"})</f>
         <v/>
       </c>
-      <c r="AP4" s="93">
+      <c r="AP4" s="94">
         <f>LOOKUP(WEEKDAY(AP5,2),{1,2,3,4,5,6,7},{"пн","вт","ср","чт","пт","сб","вс"})</f>
         <v/>
       </c>
-      <c r="AQ4" s="93">
+      <c r="AQ4" s="94">
         <f>LOOKUP(WEEKDAY(AQ5,2),{1,2,3,4,5,6,7},{"пн","вт","ср","чт","пт","сб","вс"})</f>
         <v/>
       </c>
-      <c r="AR4" s="93">
+      <c r="AR4" s="94">
         <f>LOOKUP(WEEKDAY(AR5,2),{1,2,3,4,5,6,7},{"пн","вт","ср","чт","пт","сб","вс"})</f>
         <v/>
       </c>
-      <c r="AS4" s="93">
+      <c r="AS4" s="94">
         <f>LOOKUP(WEEKDAY(AS5,2),{1,2,3,4,5,6,7},{"пн","вт","ср","чт","пт","сб","вс"})</f>
         <v/>
       </c>
-      <c r="AT4" s="93">
+      <c r="AT4" s="94">
         <f>LOOKUP(WEEKDAY(AT5,2),{1,2,3,4,5,6,7},{"пн","вт","ср","чт","пт","сб","вс"})</f>
         <v/>
       </c>
-      <c r="AU4" s="93">
+      <c r="AU4" s="94">
         <f>LOOKUP(WEEKDAY(AU5,2),{1,2,3,4,5,6,7},{"пн","вт","ср","чт","пт","сб","вс"})</f>
         <v/>
       </c>
-      <c r="AV4" s="93">
+      <c r="AV4" s="94">
         <f>LOOKUP(WEEKDAY(AV5,2),{1,2,3,4,5,6,7},{"пн","вт","ср","чт","пт","сб","вс"})</f>
         <v/>
       </c>
-      <c r="AW4" s="93">
+      <c r="AW4" s="94">
         <f>LOOKUP(WEEKDAY(AW5,2),{1,2,3,4,5,6,7},{"пн","вт","ср","чт","пт","сб","вс"})</f>
         <v/>
       </c>
-      <c r="AX4" s="93">
+      <c r="AX4" s="94">
         <f>LOOKUP(WEEKDAY(AX5,2),{1,2,3,4,5,6,7},{"пн","вт","ср","чт","пт","сб","вс"})</f>
         <v/>
       </c>
@@ -2093,7 +2093,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" s="62">
+    <row r="5" ht="26.25" customHeight="1" s="62">
       <c r="A5" s="79" t="n"/>
       <c r="B5" s="79" t="n"/>
       <c r="C5" s="79" t="n"/>
@@ -2108,220 +2108,220 @@
       <c r="L5" s="79" t="n"/>
       <c r="M5" s="79" t="n"/>
       <c r="N5" s="79" t="n"/>
-      <c r="O5" s="94" t="n">
+      <c r="O5" s="95" t="n">
         <v>46266</v>
       </c>
-      <c r="P5" s="94" t="n">
+      <c r="P5" s="95" t="n">
         <v>46267</v>
       </c>
-      <c r="Q5" s="94" t="n">
+      <c r="Q5" s="95" t="n">
         <v>46268</v>
       </c>
-      <c r="R5" s="94" t="n">
+      <c r="R5" s="95" t="n">
         <v>46269</v>
       </c>
-      <c r="S5" s="94" t="n">
+      <c r="S5" s="95" t="n">
         <v>46270</v>
       </c>
-      <c r="T5" s="94" t="n">
+      <c r="T5" s="95" t="n">
         <v>46271</v>
       </c>
-      <c r="U5" s="94" t="n">
+      <c r="U5" s="95" t="n">
         <v>46272</v>
       </c>
-      <c r="V5" s="94" t="n">
+      <c r="V5" s="95" t="n">
         <v>46273</v>
       </c>
-      <c r="W5" s="94" t="n">
+      <c r="W5" s="95" t="n">
         <v>46274</v>
       </c>
-      <c r="X5" s="94" t="n">
+      <c r="X5" s="95" t="n">
         <v>46275</v>
       </c>
-      <c r="Y5" s="94" t="n">
+      <c r="Y5" s="95" t="n">
         <v>46276</v>
       </c>
-      <c r="Z5" s="94" t="n">
+      <c r="Z5" s="95" t="n">
         <v>46277</v>
       </c>
-      <c r="AA5" s="94" t="n">
+      <c r="AA5" s="95" t="n">
         <v>46278</v>
       </c>
-      <c r="AB5" s="94" t="n">
+      <c r="AB5" s="95" t="n">
         <v>46279</v>
       </c>
-      <c r="AC5" s="94" t="n">
+      <c r="AC5" s="95" t="n">
         <v>46280</v>
       </c>
-      <c r="AD5" s="94" t="n">
+      <c r="AD5" s="95" t="n">
         <v>46281</v>
       </c>
-      <c r="AE5" s="94" t="n">
+      <c r="AE5" s="95" t="n">
         <v>46282</v>
       </c>
-      <c r="AF5" s="94" t="n">
+      <c r="AF5" s="95" t="n">
         <v>46283</v>
       </c>
-      <c r="AG5" s="94" t="n">
+      <c r="AG5" s="95" t="n">
         <v>46284</v>
       </c>
-      <c r="AH5" s="94" t="n">
+      <c r="AH5" s="95" t="n">
         <v>46285</v>
       </c>
-      <c r="AI5" s="94" t="n">
+      <c r="AI5" s="95" t="n">
         <v>46286</v>
       </c>
-      <c r="AJ5" s="94" t="n">
+      <c r="AJ5" s="95" t="n">
         <v>46287</v>
       </c>
-      <c r="AK5" s="94" t="n">
+      <c r="AK5" s="95" t="n">
         <v>46288</v>
       </c>
-      <c r="AL5" s="94" t="n">
+      <c r="AL5" s="95" t="n">
         <v>46289</v>
       </c>
-      <c r="AM5" s="94" t="n">
+      <c r="AM5" s="95" t="n">
         <v>46290</v>
       </c>
-      <c r="AN5" s="94" t="n">
+      <c r="AN5" s="95" t="n">
         <v>46291</v>
       </c>
-      <c r="AO5" s="94" t="n">
+      <c r="AO5" s="95" t="n">
         <v>46292</v>
       </c>
-      <c r="AP5" s="94" t="n">
+      <c r="AP5" s="95" t="n">
         <v>46293</v>
       </c>
-      <c r="AQ5" s="94" t="n">
+      <c r="AQ5" s="95" t="n">
         <v>46294</v>
       </c>
-      <c r="AR5" s="94" t="n">
+      <c r="AR5" s="95" t="n">
         <v>46295</v>
       </c>
-      <c r="AS5" s="94" t="n">
+      <c r="AS5" s="95" t="n">
         <v>46296</v>
       </c>
-      <c r="AT5" s="94" t="n">
+      <c r="AT5" s="95" t="n">
         <v>46297</v>
       </c>
-      <c r="AU5" s="94" t="n">
+      <c r="AU5" s="95" t="n">
         <v>46298</v>
       </c>
-      <c r="AV5" s="94" t="n">
+      <c r="AV5" s="95" t="n">
         <v>46299</v>
       </c>
-      <c r="AW5" s="94" t="n">
+      <c r="AW5" s="95" t="n">
         <v>46300</v>
       </c>
-      <c r="AX5" s="94" t="n">
+      <c r="AX5" s="95" t="n">
         <v>46301</v>
       </c>
-      <c r="AY5" s="94" t="n">
+      <c r="AY5" s="95" t="n">
         <v>46302</v>
       </c>
-      <c r="AZ5" s="94" t="n">
+      <c r="AZ5" s="95" t="n">
         <v>46303</v>
       </c>
-      <c r="BA5" s="94" t="n">
+      <c r="BA5" s="95" t="n">
         <v>46304</v>
       </c>
-      <c r="BB5" s="94" t="n">
+      <c r="BB5" s="95" t="n">
         <v>46305</v>
       </c>
-      <c r="BC5" s="94" t="n">
+      <c r="BC5" s="95" t="n">
         <v>46306</v>
       </c>
-      <c r="BD5" s="94" t="n">
+      <c r="BD5" s="95" t="n">
         <v>46307</v>
       </c>
-      <c r="BE5" s="94" t="n">
+      <c r="BE5" s="95" t="n">
         <v>46308</v>
       </c>
-      <c r="BF5" s="94" t="n">
+      <c r="BF5" s="95" t="n">
         <v>46309</v>
       </c>
-      <c r="BG5" s="94" t="n">
+      <c r="BG5" s="95" t="n">
         <v>46310</v>
       </c>
-      <c r="BH5" s="94" t="n">
+      <c r="BH5" s="95" t="n">
         <v>46311</v>
       </c>
-      <c r="BI5" s="94" t="n">
+      <c r="BI5" s="95" t="n">
         <v>46312</v>
       </c>
-      <c r="BJ5" s="94" t="n">
+      <c r="BJ5" s="95" t="n">
         <v>46313</v>
       </c>
-      <c r="BK5" s="94" t="n">
+      <c r="BK5" s="95" t="n">
         <v>46314</v>
       </c>
-      <c r="BL5" s="94" t="n">
+      <c r="BL5" s="95" t="n">
         <v>46315</v>
       </c>
-      <c r="BM5" s="94" t="n">
+      <c r="BM5" s="95" t="n">
         <v>46316</v>
       </c>
-      <c r="BN5" s="94" t="n">
+      <c r="BN5" s="95" t="n">
         <v>46317</v>
       </c>
-      <c r="BO5" s="94" t="n">
+      <c r="BO5" s="95" t="n">
         <v>46318</v>
       </c>
-      <c r="BP5" s="94" t="n">
+      <c r="BP5" s="95" t="n">
         <v>46319</v>
       </c>
-      <c r="BQ5" s="94" t="n">
+      <c r="BQ5" s="95" t="n">
         <v>46320</v>
       </c>
-      <c r="BR5" s="94" t="n">
+      <c r="BR5" s="95" t="n">
         <v>46321</v>
       </c>
-      <c r="BS5" s="94" t="n">
+      <c r="BS5" s="95" t="n">
         <v>46322</v>
       </c>
-      <c r="BT5" s="94" t="n">
+      <c r="BT5" s="95" t="n">
         <v>46323</v>
       </c>
-      <c r="BU5" s="94" t="n">
+      <c r="BU5" s="95" t="n">
         <v>46324</v>
       </c>
-      <c r="BV5" s="94" t="n">
+      <c r="BV5" s="95" t="n">
         <v>46325</v>
       </c>
-      <c r="BW5" s="94" t="n">
+      <c r="BW5" s="95" t="n">
         <v>46326</v>
       </c>
-      <c r="BX5" s="94" t="n">
+      <c r="BX5" s="95" t="n">
         <v>46327</v>
       </c>
-      <c r="BY5" s="94" t="n">
+      <c r="BY5" s="95" t="n">
         <v>46328</v>
       </c>
-      <c r="BZ5" s="94" t="n">
+      <c r="BZ5" s="95" t="n">
         <v>46329</v>
       </c>
-      <c r="CA5" s="94" t="n">
+      <c r="CA5" s="95" t="n">
         <v>46330</v>
       </c>
-      <c r="CB5" s="94" t="n">
+      <c r="CB5" s="95" t="n">
         <v>46331</v>
       </c>
-      <c r="CC5" s="94" t="n">
+      <c r="CC5" s="95" t="n">
         <v>46332</v>
       </c>
-      <c r="CD5" s="94" t="n">
+      <c r="CD5" s="95" t="n">
         <v>46333</v>
       </c>
-      <c r="CE5" s="94" t="n">
+      <c r="CE5" s="95" t="n">
         <v>46334</v>
       </c>
-      <c r="CF5" s="94" t="n">
+      <c r="CF5" s="95" t="n">
         <v>46335</v>
       </c>
-      <c r="CG5" s="94" t="n">
+      <c r="CG5" s="95" t="n">
         <v>46336</v>
       </c>
-      <c r="CH5" s="94" t="n">
+      <c r="CH5" s="95" t="n">
         <v>46337</v>
       </c>
     </row>
